--- a/sheets/대금율보/검수/그대에게 가는길.xlsx
+++ b/sheets/대금율보/검수/그대에게 가는길.xlsx
@@ -3790,7 +3790,7 @@
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">浹汰‹
+          <t xml:space="preserve">浹汰
 –無</t>
         </is>
       </c>
@@ -3931,15 +3931,11 @@
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潕‹</t>
+潕</t>
         </is>
       </c>
       <c r="K6" s="24"/>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L6" s="21"/>
       <c r="M6" s="24"/>
     </row>
     <row r="7" ht="56" customHeight="1">
@@ -4109,7 +4105,7 @@
       <c r="K10" s="24"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 浹</t>
         </is>
       </c>
@@ -4236,7 +4232,7 @@
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-淋‹</t>
+淋</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -4296,7 +4292,7 @@
       </c>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">浹汰‹
+          <t xml:space="preserve">浹汰
 –潢</t>
         </is>
       </c>
@@ -4532,7 +4528,7 @@
       <c r="D21" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潕?</t>
+潕</t>
         </is>
       </c>
       <c r="E21" s="30"/>
@@ -4566,7 +4562,7 @@
       <c r="D22" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-淋潕?</t>
+淋潕</t>
         </is>
       </c>
       <c r="E22" s="31"/>

--- a/sheets/대금율보/검수/그대에게 가는길.xlsx
+++ b/sheets/대금율보/검수/그대에게 가는길.xlsx
@@ -3731,24 +3731,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="102.56" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="91.8" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="91.8" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
       <c r="L4" s="21"/>
       <c r="M4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="91.8" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="M5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="91.8" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       <c r="L6" s="21"/>
       <c r="M6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="91.8" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="M7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="91.8" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="25" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="M8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="91.8" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="25" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="M9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="91.8" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="M10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="91.8" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="M11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="91.8" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="M12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="91.8" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4221,7 +4221,7 @@
       <c r="L13" s="21"/>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="91.8" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="25" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
       <c r="L14" s="21"/>
       <c r="M14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="91.8" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -4316,7 +4316,7 @@
       <c r="L15" s="21"/>
       <c r="M15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="91.8" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -4363,7 +4363,7 @@
       <c r="L16" s="21"/>
       <c r="M16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="91.8" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="M17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="91.8" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="24"/>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="M18" s="28"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="91.8" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="M19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="91.8" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="23"/>
@@ -4521,7 +4521,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="23"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="91.8" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="M21" s="23"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="91.8" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -4604,6 +4604,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="39"/>
 </worksheet>
 </file>